--- a/reports/2026-03-04.xlsx
+++ b/reports/2026-03-04.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Pullback Setups" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reversal Setups'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Breakout Setups'!$A$1:$U$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Breakout Immediate 1-5D'!$A$1:$U$1</definedName>
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-04 05:13 UTC</t>
+          <t>2026-03-04 19:35 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,27 +740,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$1.38</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$1.78B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$23.60M</t>
+          <t>$17.30M</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>511066437.1316084</v>
+        <v>377699068.2817479</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2872771137524548</v>
+        <v>0.2216723478433291</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04618196677846419</v>
+        <v>0.04581054780096247</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>PENGUUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -784,37 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>62.69</v>
+        <v>62.75</v>
       </c>
       <c r="F3" t="n">
-        <v>62.69</v>
+        <v>62.75</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$31.08</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$8.01B</t>
+          <t>$468.87M</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$12.42M</t>
+          <t>$5.14M</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>296244419.3100746</v>
+        <v>163758161.9400564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03697977593202079</v>
+        <v>0.3492626043015949</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04192603627412067</v>
+        <v>0.03137259951746153</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43.53</v>
+        <v>62.69</v>
       </c>
       <c r="F4" t="n">
-        <v>43.53</v>
+        <v>62.69</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$3.89</t>
+          <t>$32.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$2.47B</t>
+          <t>$8.40B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$6.46M</t>
+          <t>$12.78M</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>266936250.8636976</v>
+        <v>310986686.8513867</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1082604795099625</v>
+        <v>0.03702679074012367</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02421301399524148</v>
+        <v>0.04109149960527649</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
@@ -878,51 +878,51 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RIVERUSDT</t>
+          <t>WLDUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40.8</v>
+        <v>60.41</v>
       </c>
       <c r="F5" t="n">
-        <v>40.8</v>
+        <v>60.41</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$19.30</t>
+          <t>$0.43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$374.34M</t>
+          <t>$1.24B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$5.32M</t>
+          <t>$6.05M</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>55444702.79923537</v>
+        <v>158673823.1991923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1481141569330517</v>
+        <v>0.1279148702881356</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09596893051022687</v>
+        <v>0.03812876750379325</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -946,37 +946,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39.73</v>
+        <v>55.99</v>
       </c>
       <c r="F6" t="n">
-        <v>39.73</v>
+        <v>55.99</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$1.53</t>
+          <t>$192.83</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$2.55B</t>
+          <t>$2.08B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$6.04M</t>
+          <t>$7.44M</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>189651110.5521666</v>
+        <v>175441580.3726407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07425364553244833</v>
+        <v>0.08450489984119799</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03187070631646743</v>
+        <v>0.04239175487477431</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1000,37 +1000,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33.54</v>
+        <v>55.58</v>
       </c>
       <c r="F7" t="n">
-        <v>33.54</v>
+        <v>55.58</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$9.10</t>
+          <t>$245.20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$3.93B</t>
+          <t>$4.07B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$13.39M</t>
+          <t>$11.26M</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>316009274.7703289</v>
+        <v>365182091.7711815</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08038768312221005</v>
+        <v>0.089830043314877</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04236666202512695</v>
+        <v>0.03083869678652388</v>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>ICPUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1054,37 +1054,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33.11</v>
+        <v>54.34</v>
       </c>
       <c r="F8" t="n">
-        <v>33.11</v>
+        <v>54.34</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$110.41</t>
+          <t>$2.53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$1.70B</t>
+          <t>$1.39B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$17.09M</t>
+          <t>$5.92M</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>515105403.1097226</v>
+        <v>108378065.2605769</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3029256393226982</v>
+        <v>0.07774862498489049</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0331855695684846</v>
+        <v>0.05458817816848437</v>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1108,37 +1108,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32.34</v>
+        <v>51.87</v>
       </c>
       <c r="F9" t="n">
-        <v>32.34</v>
+        <v>51.87</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$54.64</t>
+          <t>$9.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$4.20B</t>
+          <t>$6.75B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>$12.04M</t>
+          <t>$26.93M</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>358551549.989315</v>
+        <v>940879628.552073</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08535183814537353</v>
+        <v>0.1393051686978373</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03356843709184545</v>
+        <v>0.02862104763437294</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,37 +1162,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32.02</v>
+        <v>47.51</v>
       </c>
       <c r="F10" t="n">
-        <v>32.02</v>
+        <v>47.51</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$8.73</t>
+          <t>$4.05</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$6.19B</t>
+          <t>$2.57B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$14.71M</t>
+          <t>$9.18M</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>756065766.5258785</v>
+        <v>330546504.7829462</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1222101341941726</v>
+        <v>0.1285494901769259</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01946090812524096</v>
+        <v>0.02777415092024188</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APTUSDT</t>
+          <t>BCHUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1216,37 +1216,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31.27</v>
+        <v>44.25</v>
       </c>
       <c r="F11" t="n">
-        <v>31.27</v>
+        <v>44.25</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$472.30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$783.72M</t>
+          <t>$9.47B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$7.81M</t>
+          <t>$10.75M</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>143965238.1505256</v>
+        <v>466089229.3198352</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1836954888934819</v>
+        <v>0.04920429563257789</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05427860570639753</v>
+        <v>0.02306058652263859</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>PEPEUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1270,37 +1270,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30.78</v>
+        <v>43.9</v>
       </c>
       <c r="F12" t="n">
-        <v>30.78</v>
+        <v>43.9</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$0.90</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>$3.51B</t>
+          <t>$1.55B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$20.34M</t>
+          <t>$17.64M</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>765680893.2988989</v>
+        <v>524027643.8969507</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2179819141732308</v>
+        <v>0.3373622369481441</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02656234044926147</v>
+        <v>0.03366169902238457</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1324,37 +1324,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28.06</v>
+        <v>40.67</v>
       </c>
       <c r="F13" t="n">
-        <v>28.06</v>
+        <v>40.67</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$0.26</t>
+          <t>$57.24</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$9.39B</t>
+          <t>$4.41B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$23.38M</t>
+          <t>$14.32M</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>735816199.5871814</v>
+        <v>418584069.3215315</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07834650353047308</v>
+        <v>0.09495963368254406</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03177669855246189</v>
+        <v>0.03420753853152782</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1378,37 +1378,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25.58</v>
+        <v>40.5</v>
       </c>
       <c r="F14" t="n">
-        <v>25.58</v>
+        <v>40.5</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$217.44</t>
+          <t>$9.66</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>$3.60B</t>
+          <t>$4.18B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$7.64M</t>
+          <t>$23.00M</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>278382154.810418</v>
+        <v>462183674.6384121</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07726468175870947</v>
+        <v>0.1105357976446332</v>
       </c>
       <c r="M14" t="n">
-        <v>0.027445124186222</v>
+        <v>0.04975970498307303</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -1418,57 +1418,53 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHZUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chiliz</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25.16</v>
+        <v>39.73</v>
       </c>
       <c r="F15" t="n">
-        <v>25.16</v>
+        <v>39.73</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$0.04</t>
+          <t>$1.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>$372.52M</t>
+          <t>$2.60B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>$6.94M</t>
+          <t>$7.26M</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>95086260.83704506</v>
+        <v>213024790.3901335</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2552491404739469</v>
+        <v>0.08186518798458821</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07296909262948802</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>broken_trend</t>
-        </is>
-      </c>
+        <v>0.03406675247847642</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1476,12 +1472,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PEPEUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1490,37 +1486,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>24</v>
+        <v>39.68</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>39.68</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$0.98</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$1.41B</t>
+          <t>$3.83B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>$13.00M</t>
+          <t>$29.05M</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>397386887.3579582</v>
+        <v>680228453.4687167</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2811210948359372</v>
+        <v>0.1775710172615262</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03272317558809575</v>
+        <v>0.04269907734613129</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -1530,12 +1526,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1544,42 +1540,262 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21.22</v>
+        <v>36.1</v>
       </c>
       <c r="F17" t="n">
-        <v>21.22</v>
+        <v>36.1</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$441.60</t>
+          <t>$0.11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>$8.83B</t>
+          <t>$3.01B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>$5.79M</t>
+          <t>$7.04M</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>324314451.5423678</v>
+        <v>118562812.3676688</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03671467566476129</v>
+        <v>0.03934555177150953</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01785753324422367</v>
+        <v>0.05941248185270676</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AAVEUSDT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Aave</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$117.58</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>$1.81B</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>$17.23M</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>518839709.9712507</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2861352789055501</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.03321109132328132</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HBARUSDT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hedera</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="F19" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$0.10</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>$4.44B</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>$5.22M</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>137873794.6771159</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0310769198129834</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.03788386069000348</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>APTUSDT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Aptos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>reversal</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>$1.01</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>$791.74M</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>$7.27M</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>132471806.2721825</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1673174504022734</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05488724724082535</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENAUSDT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ethena</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$0.12</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>$969.94M</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>$8.28M</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>162297380.0120109</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.16732747348979</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.05100092108466219</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N17"/>
+  <autoFilter ref="A1:N21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1739,7 +1955,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$1.38</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -1747,22 +1963,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$1.78B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>$23.60M</t>
+          <t>$17.30M</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>511066437.1316084</v>
+        <v>377699068.2817479</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2872771137524548</v>
+        <v>0.2216723478433291</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04618196677846419</v>
+        <v>0.04581054780096247</v>
       </c>
       <c r="P2" t="n">
         <v>87.84999999999999</v>
@@ -1787,17 +2003,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>PENGUUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$31.08</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -1805,37 +2021,37 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$8.01B</t>
+          <t>$468.87M</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>$12.42M</t>
+          <t>$5.14M</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>296244419.3100746</v>
+        <v>163758161.9400564</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03697977593202079</v>
+        <v>0.3492626043015949</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04192603627412067</v>
+        <v>0.03137259951746153</v>
       </c>
       <c r="P3" t="n">
-        <v>62.69</v>
+        <v>62.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>75.63</v>
+        <v>85.44</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>48.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>59.42</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
@@ -1845,17 +2061,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$3.89</t>
+          <t>$32.45</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -1863,34 +2079,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$2.47B</t>
+          <t>$8.40B</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>$6.46M</t>
+          <t>$12.78M</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>266936250.8636976</v>
+        <v>310986686.8513867</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1082604795099625</v>
+        <v>0.03702679074012367</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02421301399524148</v>
+        <v>0.04109149960527649</v>
       </c>
       <c r="P4" t="n">
-        <v>43.53</v>
+        <v>62.69</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>75.63</v>
+      </c>
+      <c r="S4" t="n">
         <v>100</v>
-      </c>
-      <c r="R4" t="n">
-        <v>78.42</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1903,17 +2119,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RIVERUSDT</t>
+          <t>WLDUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$19.30</t>
+          <t>$0.43</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -1921,37 +2137,37 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$374.34M</t>
+          <t>$1.24B</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>$5.32M</t>
+          <t>$6.05M</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>55444702.79923537</v>
+        <v>158673823.1991923</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1481141569330517</v>
+        <v>0.1279148702881356</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09596893051022687</v>
+        <v>0.03812876750379325</v>
       </c>
       <c r="P5" t="n">
-        <v>40.27</v>
+        <v>60.41</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>89.16</v>
       </c>
       <c r="S5" t="n">
-        <v>80</v>
+        <v>9.15</v>
       </c>
       <c r="T5" t="n">
-        <v>27.56</v>
+        <v>100</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
@@ -1961,17 +2177,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$1.53</t>
+          <t>$192.83</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -1979,37 +2195,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$2.55B</t>
+          <t>$2.08B</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>$6.04M</t>
+          <t>$7.44M</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>189651110.5521666</v>
+        <v>175441580.3726407</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07425364553244833</v>
+        <v>0.08450489984119799</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03187070631646743</v>
+        <v>0.04239175487477431</v>
       </c>
       <c r="P6" t="n">
-        <v>39.73</v>
+        <v>55.99</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
       </c>
       <c r="R6" t="n">
-        <v>65.78</v>
+        <v>88.27</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>33.04</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
@@ -2019,17 +2235,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$9.10</t>
+          <t>$245.20</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -2037,37 +2253,37 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$3.93B</t>
+          <t>$4.07B</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>$13.39M</t>
+          <t>$11.26M</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>316009274.7703289</v>
+        <v>365182091.7711815</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08038768312221005</v>
+        <v>0.089830043314877</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04236666202512695</v>
+        <v>0.03083869678652388</v>
       </c>
       <c r="P7" t="n">
-        <v>33.54</v>
+        <v>55.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>97.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>85.14</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U7" t="inlineStr"/>
     </row>
@@ -2077,17 +2293,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AAVEUSDT</t>
+          <t>ICPUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$110.41</t>
+          <t>$2.53</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -2095,37 +2311,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$1.70B</t>
+          <t>$1.39B</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>$17.09M</t>
+          <t>$5.92M</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>515105403.1097226</v>
+        <v>108378065.2605769</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3029256393226982</v>
+        <v>0.07774862498489049</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0331855695684846</v>
+        <v>0.05458817816848437</v>
       </c>
       <c r="P8" t="n">
-        <v>33.11</v>
+        <v>54.34</v>
       </c>
       <c r="Q8" t="n">
         <v>100</v>
       </c>
       <c r="R8" t="n">
-        <v>90.05</v>
+        <v>80.69</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="T8" t="n">
-        <v>20.33</v>
+        <v>7.11</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
@@ -2135,17 +2351,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$54.64</t>
+          <t>$9.52</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -2153,37 +2369,37 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$4.20B</t>
+          <t>$6.75B</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>$12.04M</t>
+          <t>$26.93M</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>358551549.989315</v>
+        <v>940879628.552073</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08535183814537353</v>
+        <v>0.1393051686978373</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03356843709184545</v>
+        <v>0.02862104763437294</v>
       </c>
       <c r="P9" t="n">
-        <v>32.34</v>
+        <v>51.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="R9" t="n">
-        <v>89.06999999999999</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>14.03</v>
+        <v>14.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>66.16</v>
       </c>
       <c r="U9" t="inlineStr"/>
     </row>
@@ -2193,17 +2409,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$8.73</t>
+          <t>$4.05</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -2211,37 +2427,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$6.19B</t>
+          <t>$2.57B</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>$14.71M</t>
+          <t>$9.18M</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>756065766.5258785</v>
+        <v>330546504.7829462</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1222101341941726</v>
+        <v>0.1285494901769259</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01946090812524096</v>
+        <v>0.02777415092024188</v>
       </c>
       <c r="P10" t="n">
-        <v>32.02</v>
+        <v>47.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="R10" t="n">
-        <v>86.95999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="S10" t="n">
-        <v>14.83</v>
+        <v>50</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>13.27</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
@@ -2251,17 +2467,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APTUSDT</t>
+          <t>BCHUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$472.30</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -2269,37 +2485,37 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$783.72M</t>
+          <t>$9.47B</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>$7.81M</t>
+          <t>$10.75M</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>143965238.1505256</v>
+        <v>466089229.3198352</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1836954888934819</v>
+        <v>0.04920429563257789</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05427860570639753</v>
+        <v>0.02306058652263859</v>
       </c>
       <c r="P11" t="n">
-        <v>31.27</v>
+        <v>44.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
       <c r="T11" t="n">
-        <v>37.58</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
@@ -2889,17 +3105,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$1.38</t>
+          <t>$32.45</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -2907,37 +3123,37 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>$1.78B</t>
+          <t>$8.40B</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>$23.60M</t>
+          <t>$12.78M</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>511066437.1316084</v>
+        <v>310986686.8513867</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2872771137524548</v>
+        <v>0.03702679074012367</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04618196677846419</v>
+        <v>0.04109149960527649</v>
       </c>
       <c r="P2" t="n">
-        <v>53.6</v>
+        <v>61.6</v>
       </c>
       <c r="Q2" t="n">
         <v>80</v>
       </c>
       <c r="R2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="S2" t="n">
         <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>100</v>
+        <v>8.76</v>
       </c>
       <c r="U2" t="inlineStr"/>
     </row>
@@ -2947,17 +3163,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$31.08</t>
+          <t>$1.32</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -2965,37 +3181,37 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>$8.01B</t>
+          <t>$1.70B</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>$12.42M</t>
+          <t>$17.30M</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>296244419.3100746</v>
+        <v>377699068.2817479</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03697977593202079</v>
+        <v>0.2216723478433291</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04192603627412067</v>
+        <v>0.04581054780096247</v>
       </c>
       <c r="P3" t="n">
-        <v>53.6</v>
+        <v>52</v>
       </c>
       <c r="Q3" t="n">
         <v>80</v>
       </c>
       <c r="R3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="T3" t="n">
-        <v>8.76</v>
+        <v>100</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
@@ -3005,17 +3221,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RIVERUSDT</t>
+          <t>ENAUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$19.30</t>
+          <t>$0.12</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -3023,39 +3239,43 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>$374.34M</t>
+          <t>$969.94M</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>$5.32M</t>
+          <t>$8.28M</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>55444702.79923537</v>
+        <v>162297380.0120109</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1481141569330517</v>
+        <v>0.16732747348979</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09596893051022687</v>
+        <v>0.05100092108466219</v>
       </c>
       <c r="P4" t="n">
-        <v>40.8</v>
+        <v>28.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="S4" t="n">
         <v>84</v>
       </c>
       <c r="T4" t="n">
-        <v>61.34</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>13.03</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3063,17 +3283,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHZUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chiliz</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$0.04</t>
+          <t>$9.66</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -3081,25 +3301,25 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>$372.52M</t>
+          <t>$4.18B</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>$6.94M</t>
+          <t>$23.00M</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>95086260.83704506</v>
+        <v>462183674.6384121</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2552491404739469</v>
+        <v>0.1105357976446332</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07296909262948802</v>
+        <v>0.04975970498307303</v>
       </c>
       <c r="P5" t="n">
-        <v>25.16</v>
+        <v>26.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -3108,10 +3328,10 @@
         <v>100</v>
       </c>
       <c r="S5" t="n">
-        <v>51.63</v>
+        <v>68</v>
       </c>
       <c r="T5" t="n">
-        <v>39.22</v>
+        <v>54.78</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3125,17 +3345,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>CHZUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Chiliz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$9.10</t>
+          <t>$0.04</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -3143,25 +3363,25 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>$3.93B</t>
+          <t>$389.78M</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>$13.39M</t>
+          <t>$5.52M</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>316009274.7703289</v>
+        <v>78940719.32113011</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08038768312221005</v>
+        <v>0.2025272808207505</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04236666202512695</v>
+        <v>0.06998812395266765</v>
       </c>
       <c r="P6" t="n">
-        <v>23.6</v>
+        <v>26.76</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3170,10 +3390,10 @@
         <v>100</v>
       </c>
       <c r="S6" t="n">
-        <v>36</v>
+        <v>67.63</v>
       </c>
       <c r="T6" t="n">
-        <v>10.47</v>
+        <v>53.61</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -3187,17 +3407,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTCUSDT</t>
+          <t>PENGUUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Pudgy Penguins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$54.64</t>
+          <t>$0.01</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -3205,25 +3425,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>$4.20B</t>
+          <t>$468.87M</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>$12.04M</t>
+          <t>$5.14M</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>358551549.989315</v>
+        <v>163758161.9400564</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08535183814537353</v>
+        <v>0.3492626043015949</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03356843709184545</v>
+        <v>0.03137259951746153</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>26.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3232,10 +3452,10 @@
         <v>100</v>
       </c>
       <c r="S7" t="n">
-        <v>30.03</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -3249,17 +3469,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$8.73</t>
+          <t>$192.83</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -3267,25 +3487,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>$6.19B</t>
+          <t>$2.08B</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>$14.71M</t>
+          <t>$7.44M</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>756065766.5258785</v>
+        <v>175441580.3726407</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1222101341941726</v>
+        <v>0.08450489984119799</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01946090812524096</v>
+        <v>0.04239175487477431</v>
       </c>
       <c r="P8" t="n">
-        <v>22.28</v>
+        <v>25.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -3294,10 +3514,10 @@
         <v>100</v>
       </c>
       <c r="S8" t="n">
-        <v>22.83</v>
+        <v>59</v>
       </c>
       <c r="T8" t="n">
-        <v>12.18</v>
+        <v>69.55</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -3311,17 +3531,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$1.53</t>
+          <t>$9.52</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -3329,37 +3549,37 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>$2.55B</t>
+          <t>$6.75B</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>$6.04M</t>
+          <t>$26.93M</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>189651110.5521666</v>
+        <v>940879628.552073</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07425364553244833</v>
+        <v>0.1393051686978373</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03187070631646743</v>
+        <v>0.02862104763437294</v>
       </c>
       <c r="P9" t="n">
-        <v>10.8</v>
+        <v>25.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="S9" t="n">
-        <v>28</v>
+        <v>54.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -3373,17 +3593,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APTUSDT</t>
+          <t>WLDUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.43</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -3391,37 +3611,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>$783.72M</t>
+          <t>$1.24B</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>$7.81M</t>
+          <t>$6.05M</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>143965238.1505256</v>
+        <v>158673823.1991923</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1836954888934819</v>
+        <v>0.1279148702881356</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05427860570639753</v>
+        <v>0.03812876750379325</v>
       </c>
       <c r="P10" t="n">
-        <v>8.800000000000001</v>
+        <v>24.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>68</v>
+        <v>49.15</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3435,17 +3655,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$3.89</t>
+          <t>$57.24</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -3453,37 +3673,37 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>$2.47B</t>
+          <t>$4.41B</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>$6.46M</t>
+          <t>$14.32M</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>266936250.8636976</v>
+        <v>418584069.3215315</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1082604795099625</v>
+        <v>0.09495963368254406</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02421301399524148</v>
+        <v>0.03420753853152782</v>
       </c>
       <c r="P11" t="n">
-        <v>7.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="S11" t="n">
-        <v>52</v>
+        <v>46.03</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>61.65</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
